--- a/HotGuy/Assets/Config/Excel/DanmakuContentConfig.xlsx
+++ b/HotGuy/Assets/Config/Excel/DanmakuContentConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GP\GP-TestRepo\HotGuy\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAC35AA2-35B5-444A-B600-7B7A1B033D82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A8F97E2-BA03-4BE2-8753-16FA7A227C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FoodConfig" sheetId="1" r:id="rId1"/>
@@ -133,265 +133,266 @@
     <t>比绅士今天用餐真优雅</t>
   </si>
   <si>
+    <t>这哪是吃播，这是晚宴</t>
+  </si>
+  <si>
+    <t>手：别装了我看见你了</t>
+  </si>
+  <si>
+    <t>比格：今天我是优雅绅士</t>
+  </si>
+  <si>
+    <t>刀叉用得比我都标准</t>
+  </si>
+  <si>
+    <t>隐藏在狗背后的干饭人</t>
+  </si>
+  <si>
+    <t>这波cos福瑞我给满分</t>
+  </si>
+  <si>
+    <t>表面狗绅士，背后大活人</t>
+  </si>
+  <si>
+    <t>优雅永不过时</t>
+  </si>
+  <si>
+    <t>比格：今天不拆家，只吃西餐</t>
+  </si>
+  <si>
+    <t>这饭吃得仪式感十足</t>
+  </si>
+  <si>
+    <t>手别抖！要优雅！</t>
+  </si>
+  <si>
+    <t>西装比格，全场最帅</t>
+  </si>
+  <si>
+    <t>这吃播档次直接上去了</t>
+  </si>
+  <si>
+    <t>假装自己是福瑞的一天</t>
+  </si>
+  <si>
+    <t>主人：演技不错，加鸡腿</t>
+  </si>
+  <si>
+    <t>优雅，太优雅了</t>
+  </si>
+  <si>
+    <t>比格：我只是个优雅道具</t>
+  </si>
+  <si>
+    <t>建议直接上米其林频道</t>
+  </si>
+  <si>
+    <t>比哥今天居然在吃饭没拆家！</t>
+  </si>
+  <si>
+    <t>这是吃播还是越狱现场哈哈</t>
+  </si>
+  <si>
+    <t>吃个饭都这么有戏</t>
+  </si>
+  <si>
+    <t>比格：吃饭不积极思想有问题</t>
+  </si>
+  <si>
+    <t>吧唧嘴都透着一股叛逆</t>
+  </si>
+  <si>
+    <t>吃完下一秒就开始拆了吧</t>
+  </si>
+  <si>
+    <t>难得安静的比格珍贵画面</t>
+  </si>
+  <si>
+    <t>这吃饭速度是怕被抢吗</t>
+  </si>
+  <si>
+    <t>比格干饭魂上线</t>
+  </si>
+  <si>
+    <t>吃归吃别把碗啃了</t>
+  </si>
+  <si>
+    <t>全网最皮干饭狗实锤</t>
+  </si>
+  <si>
+    <t>这小表情太欠了哈</t>
+  </si>
+  <si>
+    <t>吃饭都挡不住你的皮</t>
+  </si>
+  <si>
+    <t>比格：唯有干饭不可辜负</t>
+  </si>
+  <si>
+    <t>安静不过三秒的选手</t>
+  </si>
+  <si>
+    <t>吧唧吧唧全是戏</t>
+  </si>
+  <si>
+    <t>今天暂时放过家具</t>
+  </si>
+  <si>
+    <t>吃这么香是想攒力气拆家？</t>
+  </si>
+  <si>
+    <t>比格牌吃播主打一个狂野</t>
+  </si>
+  <si>
+    <t>救命它吃饭都好搞笑！</t>
+  </si>
+  <si>
+    <t>主人：忍你很久了！</t>
+  </si>
+  <si>
+    <t>巴掌比吃播还精彩</t>
+  </si>
+  <si>
+    <t>这一巴掌，清脆悦耳</t>
+  </si>
+  <si>
+    <t>终于有人治得了比格了</t>
+  </si>
+  <si>
+    <t>主人：我真的会谢！</t>
+  </si>
+  <si>
+    <t>比格：？？？</t>
+  </si>
+  <si>
+    <t>吃播秒变法治现场</t>
+  </si>
+  <si>
+    <t>这巴掌是全网的心声</t>
+  </si>
+  <si>
+    <t>住手！打得好！</t>
+  </si>
+  <si>
+    <t>比格：我只是尝个鲜</t>
+  </si>
+  <si>
+    <t>主人手速快到模糊</t>
+  </si>
+  <si>
+    <t>这一巴掌大快人心</t>
+  </si>
+  <si>
+    <t>比格：我错了但我不改</t>
+  </si>
+  <si>
+    <t>屏幕前我笑出声了</t>
+  </si>
+  <si>
+    <t>这才是比格正确打开方式</t>
+  </si>
+  <si>
+    <t>主人：别逼我动手</t>
+  </si>
+  <si>
+    <t>比格：突然有点懵</t>
+  </si>
+  <si>
+    <t>年度最佳制止画面</t>
+  </si>
+  <si>
+    <t>这巴掌，解气！</t>
+  </si>
+  <si>
+    <t>比格：我只是嘴馋而已！</t>
+  </si>
+  <si>
+    <t>比格：今天加餐，自助的</t>
+  </si>
+  <si>
+    <t>别拦它！这是它的零食！</t>
+  </si>
+  <si>
+    <t>完了，节目突然变味了</t>
+  </si>
+  <si>
+    <t>主人快按住！！</t>
+  </si>
+  <si>
+    <t>这一口下去，灵魂升华了</t>
+  </si>
+  <si>
+    <t>比格的美食鉴赏你不懂</t>
+  </si>
+  <si>
+    <t>救命，我真的会谢</t>
+  </si>
+  <si>
+    <t>吃播秒变重口味现场</t>
+  </si>
+  <si>
+    <t>这就是传说中的返祖行为？</t>
+  </si>
+  <si>
+    <t>别拍了快捞啊！</t>
+  </si>
+  <si>
+    <t>比格：这是我的秘制小汉堡</t>
+  </si>
+  <si>
+    <t>屏幕前的我瞳孔地震</t>
+  </si>
+  <si>
+    <t>好好的吃播，怎么就歪了</t>
+  </si>
+  <si>
+    <t>这一口，味道很上头</t>
+  </si>
+  <si>
+    <t>比格从不挑食，包括这个</t>
+  </si>
+  <si>
+    <t>快捂住眼睛！少儿不宜</t>
+  </si>
+  <si>
+    <t>它甚至吃得津津有味</t>
+  </si>
+  <si>
+    <t>主人：我真的会崩溃</t>
+  </si>
+  <si>
+    <t>比格的世界我们不懂</t>
+  </si>
+  <si>
+    <t>这波属于是比格传统艺能了</t>
+  </si>
+  <si>
+    <t>是天屎吗？</t>
+  </si>
+  <si>
+    <t>下饭</t>
+  </si>
+  <si>
+    <t>美食家狂喜</t>
+  </si>
+  <si>
+    <t>绷不住了</t>
+  </si>
+  <si>
+    <t>听屎一席话</t>
+  </si>
+  <si>
+    <t>答辩级发言</t>
+  </si>
+  <si>
+    <t>大师我悟了</t>
+  </si>
+  <si>
+    <t>啊？</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>西装一穿，格调拉满</t>
-  </si>
-  <si>
-    <t>这哪是吃播，这是晚宴</t>
-  </si>
-  <si>
-    <t>手：别装了我看见你了</t>
-  </si>
-  <si>
-    <t>比格：今天我是优雅绅士</t>
-  </si>
-  <si>
-    <t>刀叉用得比我都标准</t>
-  </si>
-  <si>
-    <t>隐藏在狗背后的干饭人</t>
-  </si>
-  <si>
-    <t>这波cos福瑞我给满分</t>
-  </si>
-  <si>
-    <t>表面狗绅士，背后大活人</t>
-  </si>
-  <si>
-    <t>优雅永不过时</t>
-  </si>
-  <si>
-    <t>比格：今天不拆家，只吃西餐</t>
-  </si>
-  <si>
-    <t>这饭吃得仪式感十足</t>
-  </si>
-  <si>
-    <t>手别抖！要优雅！</t>
-  </si>
-  <si>
-    <t>西装比格，全场最帅</t>
-  </si>
-  <si>
-    <t>这吃播档次直接上去了</t>
-  </si>
-  <si>
-    <t>假装自己是福瑞的一天</t>
-  </si>
-  <si>
-    <t>主人：演技不错，加鸡腿</t>
-  </si>
-  <si>
-    <t>优雅，太优雅了</t>
-  </si>
-  <si>
-    <t>比格：我只是个优雅道具</t>
-  </si>
-  <si>
-    <t>建议直接上米其林频道</t>
-  </si>
-  <si>
-    <t>比哥今天居然在吃饭没拆家！</t>
-  </si>
-  <si>
-    <t>这是吃播还是越狱现场哈哈</t>
-  </si>
-  <si>
-    <t>吃个饭都这么有戏</t>
-  </si>
-  <si>
-    <t>比格：吃饭不积极思想有问题</t>
-  </si>
-  <si>
-    <t>吧唧嘴都透着一股叛逆</t>
-  </si>
-  <si>
-    <t>吃完下一秒就开始拆了吧</t>
-  </si>
-  <si>
-    <t>难得安静的比格珍贵画面</t>
-  </si>
-  <si>
-    <t>这吃饭速度是怕被抢吗</t>
-  </si>
-  <si>
-    <t>比格干饭魂上线</t>
-  </si>
-  <si>
-    <t>吃归吃别把碗啃了</t>
-  </si>
-  <si>
-    <t>全网最皮干饭狗实锤</t>
-  </si>
-  <si>
-    <t>这小表情太欠了哈</t>
-  </si>
-  <si>
-    <t>吃饭都挡不住你的皮</t>
-  </si>
-  <si>
-    <t>比格：唯有干饭不可辜负</t>
-  </si>
-  <si>
-    <t>安静不过三秒的选手</t>
-  </si>
-  <si>
-    <t>吧唧吧唧全是戏</t>
-  </si>
-  <si>
-    <t>今天暂时放过家具</t>
-  </si>
-  <si>
-    <t>吃这么香是想攒力气拆家？</t>
-  </si>
-  <si>
-    <t>比格牌吃播主打一个狂野</t>
-  </si>
-  <si>
-    <t>救命它吃饭都好搞笑！</t>
-  </si>
-  <si>
-    <t>主人：忍你很久了！</t>
-  </si>
-  <si>
-    <t>巴掌比吃播还精彩</t>
-  </si>
-  <si>
-    <t>这一巴掌，清脆悦耳</t>
-  </si>
-  <si>
-    <t>终于有人治得了比格了</t>
-  </si>
-  <si>
-    <t>主人：我真的会谢！</t>
-  </si>
-  <si>
-    <t>比格：？？？</t>
-  </si>
-  <si>
-    <t>吃播秒变法治现场</t>
-  </si>
-  <si>
-    <t>这巴掌是全网的心声</t>
-  </si>
-  <si>
-    <t>住手！打得好！</t>
-  </si>
-  <si>
-    <t>比格：我只是尝个鲜</t>
-  </si>
-  <si>
-    <t>主人手速快到模糊</t>
-  </si>
-  <si>
-    <t>这一巴掌大快人心</t>
-  </si>
-  <si>
-    <t>比格：我错了但我不改</t>
-  </si>
-  <si>
-    <t>屏幕前我笑出声了</t>
-  </si>
-  <si>
-    <t>这才是比格正确打开方式</t>
-  </si>
-  <si>
-    <t>主人：别逼我动手</t>
-  </si>
-  <si>
-    <t>比格：突然有点懵</t>
-  </si>
-  <si>
-    <t>年度最佳制止画面</t>
-  </si>
-  <si>
-    <t>这巴掌，解气！</t>
-  </si>
-  <si>
-    <t>比格：我只是嘴馋而已！</t>
-  </si>
-  <si>
-    <t>比格：今天加餐，自助的</t>
-  </si>
-  <si>
-    <t>别拦它！这是它的零食！</t>
-  </si>
-  <si>
-    <t>完了，节目突然变味了</t>
-  </si>
-  <si>
-    <t>主人快按住！！</t>
-  </si>
-  <si>
-    <t>这一口下去，灵魂升华了</t>
-  </si>
-  <si>
-    <t>比格的美食鉴赏你不懂</t>
-  </si>
-  <si>
-    <t>救命，我真的会谢</t>
-  </si>
-  <si>
-    <t>吃播秒变重口味现场</t>
-  </si>
-  <si>
-    <t>这就是传说中的返祖行为？</t>
-  </si>
-  <si>
-    <t>别拍了快捞啊！</t>
-  </si>
-  <si>
-    <t>比格：这是我的秘制小汉堡</t>
-  </si>
-  <si>
-    <t>屏幕前的我瞳孔地震</t>
-  </si>
-  <si>
-    <t>好好的吃播，怎么就歪了</t>
-  </si>
-  <si>
-    <t>这一口，味道很上头</t>
-  </si>
-  <si>
-    <t>比格从不挑食，包括这个</t>
-  </si>
-  <si>
-    <t>快捂住眼睛！少儿不宜</t>
-  </si>
-  <si>
-    <t>它甚至吃得津津有味</t>
-  </si>
-  <si>
-    <t>主人：我真的会崩溃</t>
-  </si>
-  <si>
-    <t>比格的世界我们不懂</t>
-  </si>
-  <si>
-    <t>这波属于是比格传统艺能了</t>
-  </si>
-  <si>
-    <t>是天屎吗？</t>
-  </si>
-  <si>
-    <t>下饭</t>
-  </si>
-  <si>
-    <t>美食家狂喜</t>
-  </si>
-  <si>
-    <t>绷不住了</t>
-  </si>
-  <si>
-    <t>听屎一席话</t>
-  </si>
-  <si>
-    <t>答辩级发言</t>
-  </si>
-  <si>
-    <t>大师我悟了</t>
-  </si>
-  <si>
-    <t>啊？</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -514,7 +515,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1"/>
@@ -537,14 +538,13 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -861,18 +861,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G107"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.4" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="21.06640625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="21.796875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="30.796875" style="3" customWidth="1"/>
+    <col min="1" max="2" width="21.08984375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="21.81640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="30.81640625" style="3" customWidth="1"/>
     <col min="5" max="5" width="15" style="4" customWidth="1"/>
-    <col min="6" max="6" width="15.73046875" style="4" customWidth="1"/>
-    <col min="7" max="7" width="28.46484375" style="4" customWidth="1"/>
+    <col min="6" max="6" width="15.7265625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="28.453125" style="4" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -885,30 +885,30 @@
       <c r="D1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="G1" s="6"/>
     </row>
-    <row r="2" spans="1:7" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="15" t="s">
+      <c r="D2" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="14" t="s">
         <v>8</v>
       </c>
       <c r="G2" s="7"/>
     </row>
-    <row r="3" spans="1:7" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -921,18 +921,18 @@
       <c r="D3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.35">
       <c r="B4" s="4">
         <v>1</v>
       </c>
       <c r="C4" s="11">
         <v>0</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="15" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="4">
@@ -940,14 +940,14 @@
       </c>
       <c r="G4" s="8"/>
     </row>
-    <row r="5" spans="1:7" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.35">
       <c r="B5" s="4">
         <v>2</v>
       </c>
       <c r="C5" s="11">
         <v>0</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="15" t="s">
         <v>14</v>
       </c>
       <c r="E5" s="4">
@@ -955,14 +955,14 @@
       </c>
       <c r="G5" s="8"/>
     </row>
-    <row r="6" spans="1:7" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.35">
       <c r="B6" s="4">
         <v>3</v>
       </c>
       <c r="C6" s="11">
         <v>0</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="15" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="4">
@@ -970,7 +970,7 @@
       </c>
       <c r="G6" s="9"/>
     </row>
-    <row r="7" spans="1:7" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.35">
       <c r="A7" s="5"/>
       <c r="B7" s="4">
         <v>4</v>
@@ -978,7 +978,7 @@
       <c r="C7" s="11">
         <v>0</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="15" t="s">
         <v>16</v>
       </c>
       <c r="E7" s="4">
@@ -986,14 +986,14 @@
       </c>
       <c r="G7" s="8"/>
     </row>
-    <row r="8" spans="1:7" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.35">
       <c r="B8" s="4">
         <v>5</v>
       </c>
       <c r="C8" s="11">
         <v>0</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="15" t="s">
         <v>17</v>
       </c>
       <c r="E8" s="4">
@@ -1001,14 +1001,14 @@
       </c>
       <c r="G8" s="8"/>
     </row>
-    <row r="9" spans="1:7" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.35">
       <c r="B9" s="4">
         <v>6</v>
       </c>
       <c r="C9" s="11">
         <v>0</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="15" t="s">
         <v>18</v>
       </c>
       <c r="E9" s="4">
@@ -1016,14 +1016,14 @@
       </c>
       <c r="G9" s="8"/>
     </row>
-    <row r="10" spans="1:7" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.35">
       <c r="B10" s="4">
         <v>7</v>
       </c>
       <c r="C10" s="11">
         <v>0</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="15" t="s">
         <v>19</v>
       </c>
       <c r="E10" s="4">
@@ -1031,14 +1031,14 @@
       </c>
       <c r="G10" s="8"/>
     </row>
-    <row r="11" spans="1:7" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.35">
       <c r="B11" s="4">
         <v>8</v>
       </c>
       <c r="C11" s="11">
         <v>0</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="15" t="s">
         <v>20</v>
       </c>
       <c r="E11" s="4">
@@ -1046,14 +1046,14 @@
       </c>
       <c r="G11" s="8"/>
     </row>
-    <row r="12" spans="1:7" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.35">
       <c r="B12" s="4">
         <v>9</v>
       </c>
       <c r="C12" s="11">
         <v>0</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="15" t="s">
         <v>21</v>
       </c>
       <c r="E12" s="4">
@@ -1061,14 +1061,14 @@
       </c>
       <c r="G12" s="8"/>
     </row>
-    <row r="13" spans="1:7" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.35">
       <c r="B13" s="4">
         <v>10</v>
       </c>
       <c r="C13" s="11">
         <v>0</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="15" t="s">
         <v>22</v>
       </c>
       <c r="E13" s="4">
@@ -1076,14 +1076,14 @@
       </c>
       <c r="G13" s="8"/>
     </row>
-    <row r="14" spans="1:7" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.35">
       <c r="B14" s="4">
         <v>11</v>
       </c>
       <c r="C14" s="11">
         <v>0</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="15" t="s">
         <v>23</v>
       </c>
       <c r="E14" s="4">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G14" s="8"/>
     </row>
-    <row r="15" spans="1:7" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.35">
       <c r="B15" s="4">
         <v>12</v>
       </c>
       <c r="C15" s="11">
         <v>0</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="15" t="s">
         <v>24</v>
       </c>
       <c r="E15" s="4">
@@ -1106,14 +1106,14 @@
       </c>
       <c r="G15" s="8"/>
     </row>
-    <row r="16" spans="1:7" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.35">
       <c r="B16" s="4">
         <v>13</v>
       </c>
       <c r="C16" s="11">
         <v>0</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="15" t="s">
         <v>25</v>
       </c>
       <c r="E16" s="4">
@@ -1121,14 +1121,14 @@
       </c>
       <c r="G16" s="8"/>
     </row>
-    <row r="17" spans="2:7" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:7" ht="15" x14ac:dyDescent="0.35">
       <c r="B17" s="4">
         <v>14</v>
       </c>
       <c r="C17" s="11">
         <v>0</v>
       </c>
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="15" t="s">
         <v>26</v>
       </c>
       <c r="E17" s="4">
@@ -1136,1261 +1136,1261 @@
       </c>
       <c r="G17" s="8"/>
     </row>
-    <row r="18" spans="2:7" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:7" ht="15" x14ac:dyDescent="0.35">
       <c r="B18" s="4">
         <v>15</v>
       </c>
       <c r="C18" s="11">
         <v>0</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="15" t="s">
         <v>27</v>
       </c>
       <c r="E18" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:7" ht="15" x14ac:dyDescent="0.35">
       <c r="B19" s="4">
         <v>16</v>
       </c>
       <c r="C19" s="11">
         <v>0</v>
       </c>
-      <c r="D19" s="16" t="s">
+      <c r="D19" s="15" t="s">
         <v>28</v>
       </c>
       <c r="E19" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="2:7" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:7" ht="15" x14ac:dyDescent="0.35">
       <c r="B20" s="4">
         <v>17</v>
       </c>
       <c r="C20" s="11">
         <v>0</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="15" t="s">
         <v>29</v>
       </c>
       <c r="E20" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="2:7" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:7" ht="15" x14ac:dyDescent="0.35">
       <c r="B21" s="4">
         <v>18</v>
       </c>
       <c r="C21" s="11">
         <v>0</v>
       </c>
-      <c r="D21" s="16" t="s">
-        <v>30</v>
+      <c r="D21" s="15" t="s">
+        <v>116</v>
       </c>
       <c r="E21" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:7" ht="15" x14ac:dyDescent="0.35">
       <c r="B22" s="4">
         <v>19</v>
       </c>
       <c r="C22" s="11">
         <v>0</v>
       </c>
-      <c r="D22" s="16" t="s">
-        <v>31</v>
+      <c r="D22" s="15" t="s">
+        <v>30</v>
       </c>
       <c r="E22" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="2:7" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:7" ht="15" x14ac:dyDescent="0.35">
       <c r="B23" s="4">
         <v>20</v>
       </c>
       <c r="C23" s="11">
         <v>0</v>
       </c>
-      <c r="D23" s="16" t="s">
-        <v>32</v>
+      <c r="D23" s="15" t="s">
+        <v>31</v>
       </c>
       <c r="E23" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="2:7" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:7" ht="15" x14ac:dyDescent="0.35">
       <c r="B24" s="4">
         <v>21</v>
       </c>
       <c r="C24" s="11">
         <v>0</v>
       </c>
-      <c r="D24" s="16" t="s">
-        <v>33</v>
+      <c r="D24" s="15" t="s">
+        <v>32</v>
       </c>
       <c r="E24" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="2:7" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:7" ht="15" x14ac:dyDescent="0.35">
       <c r="B25" s="4">
         <v>22</v>
       </c>
       <c r="C25" s="11">
         <v>0</v>
       </c>
-      <c r="D25" s="16" t="s">
-        <v>34</v>
+      <c r="D25" s="15" t="s">
+        <v>33</v>
       </c>
       <c r="E25" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:7" ht="15" x14ac:dyDescent="0.35">
       <c r="B26" s="4">
         <v>23</v>
       </c>
       <c r="C26" s="11">
         <v>0</v>
       </c>
-      <c r="D26" s="16" t="s">
-        <v>35</v>
+      <c r="D26" s="15" t="s">
+        <v>34</v>
       </c>
       <c r="E26" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="2:7" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:7" ht="15" x14ac:dyDescent="0.35">
       <c r="B27" s="4">
         <v>24</v>
       </c>
       <c r="C27" s="11">
         <v>0</v>
       </c>
-      <c r="D27" s="16" t="s">
-        <v>36</v>
+      <c r="D27" s="15" t="s">
+        <v>35</v>
       </c>
       <c r="E27" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:7" ht="15" x14ac:dyDescent="0.35">
       <c r="B28" s="4">
         <v>25</v>
       </c>
       <c r="C28" s="11">
         <v>0</v>
       </c>
-      <c r="D28" s="16" t="s">
-        <v>37</v>
+      <c r="D28" s="15" t="s">
+        <v>36</v>
       </c>
       <c r="E28" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="2:7" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:7" ht="15" x14ac:dyDescent="0.35">
       <c r="B29" s="4">
         <v>26</v>
       </c>
       <c r="C29" s="11">
         <v>0</v>
       </c>
-      <c r="D29" s="16" t="s">
-        <v>38</v>
+      <c r="D29" s="15" t="s">
+        <v>37</v>
       </c>
       <c r="E29" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="2:7" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:7" ht="15" x14ac:dyDescent="0.35">
       <c r="B30" s="4">
         <v>27</v>
       </c>
       <c r="C30" s="11">
         <v>0</v>
       </c>
-      <c r="D30" s="16" t="s">
-        <v>39</v>
+      <c r="D30" s="15" t="s">
+        <v>38</v>
       </c>
       <c r="E30" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="2:7" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:7" ht="15" x14ac:dyDescent="0.35">
       <c r="B31" s="4">
         <v>28</v>
       </c>
       <c r="C31" s="11">
         <v>0</v>
       </c>
-      <c r="D31" s="16" t="s">
-        <v>40</v>
+      <c r="D31" s="15" t="s">
+        <v>39</v>
       </c>
       <c r="E31" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="2:7" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:7" ht="15" x14ac:dyDescent="0.35">
       <c r="B32" s="4">
         <v>29</v>
       </c>
       <c r="C32" s="11">
         <v>0</v>
       </c>
-      <c r="D32" s="16" t="s">
-        <v>41</v>
+      <c r="D32" s="15" t="s">
+        <v>40</v>
       </c>
       <c r="E32" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B33" s="4">
         <v>30</v>
       </c>
       <c r="C33" s="11">
         <v>0</v>
       </c>
-      <c r="D33" s="16" t="s">
-        <v>42</v>
+      <c r="D33" s="15" t="s">
+        <v>41</v>
       </c>
       <c r="E33" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B34" s="4">
         <v>31</v>
       </c>
       <c r="C34" s="11">
         <v>0</v>
       </c>
-      <c r="D34" s="16" t="s">
-        <v>43</v>
+      <c r="D34" s="15" t="s">
+        <v>42</v>
       </c>
       <c r="E34" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B35" s="4">
         <v>32</v>
       </c>
       <c r="C35" s="11">
         <v>0</v>
       </c>
-      <c r="D35" s="16" t="s">
-        <v>44</v>
+      <c r="D35" s="15" t="s">
+        <v>43</v>
       </c>
       <c r="E35" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B36" s="4">
         <v>33</v>
       </c>
       <c r="C36" s="11">
         <v>0</v>
       </c>
-      <c r="D36" s="16" t="s">
-        <v>45</v>
+      <c r="D36" s="15" t="s">
+        <v>44</v>
       </c>
       <c r="E36" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B37" s="4">
         <v>34</v>
       </c>
       <c r="C37" s="11">
         <v>0</v>
       </c>
-      <c r="D37" s="16" t="s">
-        <v>46</v>
+      <c r="D37" s="15" t="s">
+        <v>45</v>
       </c>
       <c r="E37" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B38" s="4">
         <v>35</v>
       </c>
       <c r="C38" s="11">
         <v>0</v>
       </c>
-      <c r="D38" s="16" t="s">
-        <v>47</v>
+      <c r="D38" s="15" t="s">
+        <v>46</v>
       </c>
       <c r="E38" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B39" s="4">
         <v>36</v>
       </c>
       <c r="C39" s="11">
         <v>0</v>
       </c>
-      <c r="D39" s="16" t="s">
-        <v>48</v>
+      <c r="D39" s="15" t="s">
+        <v>47</v>
       </c>
       <c r="E39" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B40" s="4">
         <v>37</v>
       </c>
       <c r="C40" s="11">
         <v>1</v>
       </c>
-      <c r="D40" s="16" t="s">
-        <v>49</v>
+      <c r="D40" s="15" t="s">
+        <v>48</v>
       </c>
       <c r="E40" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B41" s="4">
         <v>38</v>
       </c>
       <c r="C41" s="11">
         <v>1</v>
       </c>
-      <c r="D41" s="16" t="s">
-        <v>50</v>
+      <c r="D41" s="15" t="s">
+        <v>49</v>
       </c>
       <c r="E41" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B42" s="4">
         <v>39</v>
       </c>
       <c r="C42" s="11">
         <v>1</v>
       </c>
-      <c r="D42" s="16" t="s">
-        <v>51</v>
+      <c r="D42" s="15" t="s">
+        <v>50</v>
       </c>
       <c r="E42" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B43" s="4">
         <v>40</v>
       </c>
       <c r="C43" s="11">
         <v>1</v>
       </c>
-      <c r="D43" s="16" t="s">
-        <v>52</v>
+      <c r="D43" s="15" t="s">
+        <v>51</v>
       </c>
       <c r="E43" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B44" s="4">
         <v>41</v>
       </c>
       <c r="C44" s="11">
         <v>1</v>
       </c>
-      <c r="D44" s="16" t="s">
-        <v>53</v>
+      <c r="D44" s="15" t="s">
+        <v>52</v>
       </c>
       <c r="E44" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B45" s="4">
         <v>42</v>
       </c>
       <c r="C45" s="11">
         <v>1</v>
       </c>
-      <c r="D45" s="16" t="s">
-        <v>54</v>
+      <c r="D45" s="15" t="s">
+        <v>53</v>
       </c>
       <c r="E45" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B46" s="4">
         <v>43</v>
       </c>
       <c r="C46" s="11">
         <v>1</v>
       </c>
-      <c r="D46" s="16" t="s">
-        <v>55</v>
+      <c r="D46" s="15" t="s">
+        <v>54</v>
       </c>
       <c r="E46" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B47" s="4">
         <v>44</v>
       </c>
       <c r="C47" s="11">
         <v>1</v>
       </c>
-      <c r="D47" s="16" t="s">
-        <v>56</v>
+      <c r="D47" s="15" t="s">
+        <v>55</v>
       </c>
       <c r="E47" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B48" s="4">
         <v>45</v>
       </c>
       <c r="C48" s="11">
         <v>1</v>
       </c>
-      <c r="D48" s="16" t="s">
-        <v>57</v>
+      <c r="D48" s="15" t="s">
+        <v>56</v>
       </c>
       <c r="E48" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="49" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B49" s="4">
         <v>46</v>
       </c>
       <c r="C49" s="11">
         <v>1</v>
       </c>
-      <c r="D49" s="16" t="s">
-        <v>58</v>
+      <c r="D49" s="15" t="s">
+        <v>57</v>
       </c>
       <c r="E49" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="50" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B50" s="4">
         <v>47</v>
       </c>
       <c r="C50" s="11">
         <v>1</v>
       </c>
-      <c r="D50" s="16" t="s">
-        <v>59</v>
+      <c r="D50" s="15" t="s">
+        <v>58</v>
       </c>
       <c r="E50" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B51" s="4">
         <v>48</v>
       </c>
       <c r="C51" s="11">
         <v>1</v>
       </c>
-      <c r="D51" s="16" t="s">
-        <v>60</v>
+      <c r="D51" s="15" t="s">
+        <v>59</v>
       </c>
       <c r="E51" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B52" s="4">
         <v>49</v>
       </c>
       <c r="C52" s="11">
         <v>1</v>
       </c>
-      <c r="D52" s="16" t="s">
-        <v>61</v>
+      <c r="D52" s="15" t="s">
+        <v>60</v>
       </c>
       <c r="E52" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B53" s="4">
         <v>50</v>
       </c>
       <c r="C53" s="11">
         <v>1</v>
       </c>
-      <c r="D53" s="16" t="s">
-        <v>62</v>
+      <c r="D53" s="15" t="s">
+        <v>61</v>
       </c>
       <c r="E53" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B54" s="4">
         <v>51</v>
       </c>
       <c r="C54" s="11">
         <v>1</v>
       </c>
-      <c r="D54" s="16" t="s">
-        <v>63</v>
+      <c r="D54" s="15" t="s">
+        <v>62</v>
       </c>
       <c r="E54" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="55" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B55" s="4">
         <v>52</v>
       </c>
       <c r="C55" s="11">
         <v>1</v>
       </c>
-      <c r="D55" s="16" t="s">
-        <v>64</v>
+      <c r="D55" s="15" t="s">
+        <v>63</v>
       </c>
       <c r="E55" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="56" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B56" s="4">
         <v>53</v>
       </c>
       <c r="C56" s="11">
         <v>1</v>
       </c>
-      <c r="D56" s="16" t="s">
-        <v>65</v>
+      <c r="D56" s="15" t="s">
+        <v>64</v>
       </c>
       <c r="E56" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="57" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B57" s="4">
         <v>54</v>
       </c>
       <c r="C57" s="11">
         <v>1</v>
       </c>
-      <c r="D57" s="16" t="s">
-        <v>66</v>
+      <c r="D57" s="15" t="s">
+        <v>65</v>
       </c>
       <c r="E57" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="58" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B58" s="4">
         <v>55</v>
       </c>
       <c r="C58" s="11">
         <v>1</v>
       </c>
-      <c r="D58" s="16" t="s">
-        <v>67</v>
+      <c r="D58" s="15" t="s">
+        <v>66</v>
       </c>
       <c r="E58" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="59" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B59" s="4">
         <v>56</v>
       </c>
       <c r="C59" s="11">
         <v>1</v>
       </c>
-      <c r="D59" s="16" t="s">
-        <v>68</v>
+      <c r="D59" s="15" t="s">
+        <v>67</v>
       </c>
       <c r="E59" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="60" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="60" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B60" s="4">
         <v>57</v>
       </c>
-      <c r="C60" s="17">
+      <c r="C60" s="16">
         <v>2</v>
       </c>
-      <c r="D60" s="16" t="s">
-        <v>69</v>
+      <c r="D60" s="15" t="s">
+        <v>68</v>
       </c>
       <c r="E60" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="61" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="61" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B61" s="4">
         <v>58</v>
       </c>
-      <c r="C61" s="17">
+      <c r="C61" s="16">
         <v>2</v>
       </c>
-      <c r="D61" s="16" t="s">
-        <v>70</v>
+      <c r="D61" s="15" t="s">
+        <v>69</v>
       </c>
       <c r="E61" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="62" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B62" s="4">
         <v>59</v>
       </c>
-      <c r="C62" s="17">
+      <c r="C62" s="16">
         <v>2</v>
       </c>
-      <c r="D62" s="16" t="s">
-        <v>71</v>
+      <c r="D62" s="15" t="s">
+        <v>70</v>
       </c>
       <c r="E62" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="63" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="63" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B63" s="4">
         <v>60</v>
       </c>
-      <c r="C63" s="17">
+      <c r="C63" s="16">
         <v>2</v>
       </c>
-      <c r="D63" s="16" t="s">
-        <v>72</v>
+      <c r="D63" s="15" t="s">
+        <v>71</v>
       </c>
       <c r="E63" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="64" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B64" s="4">
         <v>61</v>
       </c>
-      <c r="C64" s="17">
+      <c r="C64" s="16">
         <v>2</v>
       </c>
-      <c r="D64" s="16" t="s">
-        <v>73</v>
+      <c r="D64" s="15" t="s">
+        <v>72</v>
       </c>
       <c r="E64" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="65" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="65" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B65" s="4">
         <v>62</v>
       </c>
-      <c r="C65" s="17">
+      <c r="C65" s="16">
         <v>2</v>
       </c>
-      <c r="D65" s="16" t="s">
-        <v>74</v>
+      <c r="D65" s="15" t="s">
+        <v>73</v>
       </c>
       <c r="E65" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="66" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B66" s="4">
         <v>63</v>
       </c>
-      <c r="C66" s="17">
+      <c r="C66" s="16">
         <v>2</v>
       </c>
-      <c r="D66" s="16" t="s">
-        <v>75</v>
+      <c r="D66" s="15" t="s">
+        <v>74</v>
       </c>
       <c r="E66" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="67" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="67" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B67" s="4">
         <v>64</v>
       </c>
-      <c r="C67" s="17">
+      <c r="C67" s="16">
         <v>2</v>
       </c>
-      <c r="D67" s="16" t="s">
-        <v>76</v>
+      <c r="D67" s="15" t="s">
+        <v>75</v>
       </c>
       <c r="E67" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="68" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="68" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B68" s="4">
         <v>65</v>
       </c>
-      <c r="C68" s="17">
+      <c r="C68" s="16">
         <v>2</v>
       </c>
-      <c r="D68" s="16" t="s">
-        <v>77</v>
+      <c r="D68" s="15" t="s">
+        <v>76</v>
       </c>
       <c r="E68" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="69" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B69" s="4">
         <v>66</v>
       </c>
-      <c r="C69" s="17">
+      <c r="C69" s="16">
         <v>2</v>
       </c>
-      <c r="D69" s="16" t="s">
-        <v>78</v>
+      <c r="D69" s="15" t="s">
+        <v>77</v>
       </c>
       <c r="E69" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="70" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B70" s="4">
         <v>67</v>
       </c>
-      <c r="C70" s="17">
+      <c r="C70" s="16">
         <v>2</v>
       </c>
-      <c r="D70" s="16" t="s">
-        <v>79</v>
+      <c r="D70" s="15" t="s">
+        <v>78</v>
       </c>
       <c r="E70" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="71" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B71" s="4">
         <v>68</v>
       </c>
-      <c r="C71" s="17">
+      <c r="C71" s="16">
         <v>2</v>
       </c>
-      <c r="D71" s="16" t="s">
-        <v>80</v>
+      <c r="D71" s="15" t="s">
+        <v>79</v>
       </c>
       <c r="E71" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="72" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B72" s="4">
         <v>69</v>
       </c>
-      <c r="C72" s="17">
+      <c r="C72" s="16">
         <v>2</v>
       </c>
-      <c r="D72" s="16" t="s">
-        <v>81</v>
+      <c r="D72" s="15" t="s">
+        <v>80</v>
       </c>
       <c r="E72" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="73" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="73" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B73" s="4">
         <v>70</v>
       </c>
-      <c r="C73" s="17">
+      <c r="C73" s="16">
         <v>2</v>
       </c>
-      <c r="D73" s="16" t="s">
-        <v>82</v>
+      <c r="D73" s="15" t="s">
+        <v>81</v>
       </c>
       <c r="E73" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="74" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B74" s="4">
         <v>71</v>
       </c>
-      <c r="C74" s="17">
+      <c r="C74" s="16">
         <v>2</v>
       </c>
-      <c r="D74" s="16" t="s">
-        <v>83</v>
+      <c r="D74" s="15" t="s">
+        <v>82</v>
       </c>
       <c r="E74" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="75" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B75" s="4">
         <v>72</v>
       </c>
-      <c r="C75" s="17">
+      <c r="C75" s="16">
         <v>2</v>
       </c>
-      <c r="D75" s="16" t="s">
-        <v>84</v>
+      <c r="D75" s="15" t="s">
+        <v>83</v>
       </c>
       <c r="E75" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="76" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="76" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B76" s="4">
         <v>73</v>
       </c>
-      <c r="C76" s="17">
+      <c r="C76" s="16">
         <v>2</v>
       </c>
-      <c r="D76" s="16" t="s">
-        <v>85</v>
+      <c r="D76" s="15" t="s">
+        <v>84</v>
       </c>
       <c r="E76" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="77" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B77" s="4">
         <v>74</v>
       </c>
-      <c r="C77" s="17">
+      <c r="C77" s="16">
         <v>2</v>
       </c>
-      <c r="D77" s="16" t="s">
-        <v>86</v>
+      <c r="D77" s="15" t="s">
+        <v>85</v>
       </c>
       <c r="E77" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="78" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="78" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B78" s="4">
         <v>75</v>
       </c>
-      <c r="C78" s="17">
+      <c r="C78" s="16">
         <v>2</v>
       </c>
-      <c r="D78" s="16" t="s">
-        <v>87</v>
+      <c r="D78" s="15" t="s">
+        <v>86</v>
       </c>
       <c r="E78" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="79" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B79" s="4">
         <v>76</v>
       </c>
-      <c r="C79" s="17">
+      <c r="C79" s="16">
         <v>2</v>
       </c>
-      <c r="D79" s="16" t="s">
-        <v>88</v>
+      <c r="D79" s="15" t="s">
+        <v>87</v>
       </c>
       <c r="E79" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="80" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="80" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B80" s="4">
         <v>77</v>
       </c>
-      <c r="C80" s="18">
+      <c r="C80" s="17">
         <v>3</v>
       </c>
-      <c r="D80" s="16" t="s">
-        <v>89</v>
+      <c r="D80" s="15" t="s">
+        <v>88</v>
       </c>
       <c r="E80" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="81" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="81" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B81" s="4">
         <v>78</v>
       </c>
-      <c r="C81" s="18">
+      <c r="C81" s="17">
         <v>3</v>
       </c>
-      <c r="D81" s="16" t="s">
-        <v>90</v>
+      <c r="D81" s="15" t="s">
+        <v>89</v>
       </c>
       <c r="E81" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="82" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="82" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B82" s="4">
         <v>79</v>
       </c>
-      <c r="C82" s="18">
+      <c r="C82" s="17">
         <v>3</v>
       </c>
-      <c r="D82" s="16" t="s">
-        <v>91</v>
+      <c r="D82" s="15" t="s">
+        <v>90</v>
       </c>
       <c r="E82" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="83" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="83" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B83" s="4">
         <v>80</v>
       </c>
-      <c r="C83" s="18">
+      <c r="C83" s="17">
         <v>3</v>
       </c>
-      <c r="D83" s="16" t="s">
-        <v>92</v>
+      <c r="D83" s="15" t="s">
+        <v>91</v>
       </c>
       <c r="E83" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="84" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="84" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B84" s="4">
         <v>81</v>
       </c>
-      <c r="C84" s="18">
+      <c r="C84" s="17">
         <v>3</v>
       </c>
-      <c r="D84" s="16" t="s">
-        <v>93</v>
+      <c r="D84" s="15" t="s">
+        <v>92</v>
       </c>
       <c r="E84" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="85" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="85" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B85" s="4">
         <v>82</v>
       </c>
-      <c r="C85" s="18">
+      <c r="C85" s="17">
         <v>3</v>
       </c>
-      <c r="D85" s="16" t="s">
-        <v>94</v>
+      <c r="D85" s="15" t="s">
+        <v>93</v>
       </c>
       <c r="E85" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="86" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="86" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B86" s="4">
         <v>83</v>
       </c>
-      <c r="C86" s="18">
+      <c r="C86" s="17">
         <v>3</v>
       </c>
-      <c r="D86" s="16" t="s">
-        <v>95</v>
+      <c r="D86" s="15" t="s">
+        <v>94</v>
       </c>
       <c r="E86" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="87" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="87" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B87" s="4">
         <v>84</v>
       </c>
-      <c r="C87" s="18">
+      <c r="C87" s="17">
         <v>3</v>
       </c>
-      <c r="D87" s="16" t="s">
-        <v>96</v>
+      <c r="D87" s="15" t="s">
+        <v>95</v>
       </c>
       <c r="E87" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="88" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B88" s="4">
         <v>85</v>
       </c>
-      <c r="C88" s="18">
+      <c r="C88" s="17">
         <v>3</v>
       </c>
-      <c r="D88" s="16" t="s">
-        <v>97</v>
+      <c r="D88" s="15" t="s">
+        <v>96</v>
       </c>
       <c r="E88" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="89" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B89" s="4">
         <v>86</v>
       </c>
-      <c r="C89" s="18">
+      <c r="C89" s="17">
         <v>3</v>
       </c>
-      <c r="D89" s="16" t="s">
-        <v>98</v>
+      <c r="D89" s="15" t="s">
+        <v>97</v>
       </c>
       <c r="E89" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="90" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B90" s="4">
         <v>87</v>
       </c>
-      <c r="C90" s="18">
+      <c r="C90" s="17">
         <v>3</v>
       </c>
-      <c r="D90" s="16" t="s">
-        <v>99</v>
+      <c r="D90" s="15" t="s">
+        <v>98</v>
       </c>
       <c r="E90" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="91" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="91" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B91" s="4">
         <v>88</v>
       </c>
-      <c r="C91" s="18">
+      <c r="C91" s="17">
         <v>3</v>
       </c>
-      <c r="D91" s="16" t="s">
-        <v>100</v>
+      <c r="D91" s="15" t="s">
+        <v>99</v>
       </c>
       <c r="E91" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="92" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="92" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B92" s="4">
         <v>89</v>
       </c>
-      <c r="C92" s="18">
+      <c r="C92" s="17">
         <v>3</v>
       </c>
-      <c r="D92" s="16" t="s">
-        <v>101</v>
+      <c r="D92" s="15" t="s">
+        <v>100</v>
       </c>
       <c r="E92" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="93" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="93" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B93" s="4">
         <v>90</v>
       </c>
-      <c r="C93" s="18">
+      <c r="C93" s="17">
         <v>3</v>
       </c>
-      <c r="D93" s="16" t="s">
-        <v>102</v>
+      <c r="D93" s="15" t="s">
+        <v>101</v>
       </c>
       <c r="E93" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="94" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="94" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B94" s="4">
         <v>91</v>
       </c>
-      <c r="C94" s="18">
+      <c r="C94" s="17">
         <v>3</v>
       </c>
-      <c r="D94" s="16" t="s">
-        <v>103</v>
+      <c r="D94" s="15" t="s">
+        <v>102</v>
       </c>
       <c r="E94" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="95" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B95" s="4">
         <v>92</v>
       </c>
-      <c r="C95" s="18">
+      <c r="C95" s="17">
         <v>3</v>
       </c>
-      <c r="D95" s="16" t="s">
-        <v>104</v>
+      <c r="D95" s="15" t="s">
+        <v>103</v>
       </c>
       <c r="E95" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="96" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="96" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B96" s="4">
         <v>93</v>
       </c>
-      <c r="C96" s="18">
+      <c r="C96" s="17">
         <v>3</v>
       </c>
-      <c r="D96" s="16" t="s">
-        <v>105</v>
+      <c r="D96" s="15" t="s">
+        <v>104</v>
       </c>
       <c r="E96" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="97" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B97" s="4">
         <v>94</v>
       </c>
-      <c r="C97" s="18">
+      <c r="C97" s="17">
         <v>3</v>
       </c>
-      <c r="D97" s="16" t="s">
-        <v>106</v>
+      <c r="D97" s="15" t="s">
+        <v>105</v>
       </c>
       <c r="E97" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="98" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="98" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B98" s="4">
         <v>95</v>
       </c>
-      <c r="C98" s="18">
+      <c r="C98" s="17">
         <v>3</v>
       </c>
-      <c r="D98" s="16" t="s">
-        <v>107</v>
+      <c r="D98" s="15" t="s">
+        <v>106</v>
       </c>
       <c r="E98" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="99" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="99" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B99" s="4">
         <v>96</v>
       </c>
-      <c r="C99" s="18">
+      <c r="C99" s="17">
         <v>3</v>
       </c>
-      <c r="D99" s="16" t="s">
-        <v>108</v>
+      <c r="D99" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="E99" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="100" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="100" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B100" s="4">
         <v>97</v>
       </c>
-      <c r="C100" s="17">
+      <c r="C100" s="16">
         <v>4</v>
       </c>
-      <c r="D100" s="16" t="s">
-        <v>109</v>
+      <c r="D100" s="15" t="s">
+        <v>108</v>
       </c>
       <c r="E100" s="4">
         <v>20</v>
       </c>
     </row>
-    <row r="101" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="101" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B101" s="4">
         <v>98</v>
       </c>
-      <c r="C101" s="17">
+      <c r="C101" s="16">
         <v>4</v>
       </c>
-      <c r="D101" s="16" t="s">
-        <v>116</v>
+      <c r="D101" s="15" t="s">
+        <v>115</v>
       </c>
       <c r="E101" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="102" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="102" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B102" s="4">
         <v>99</v>
       </c>
-      <c r="C102" s="17">
+      <c r="C102" s="16">
         <v>4</v>
       </c>
-      <c r="D102" s="16" t="s">
-        <v>110</v>
+      <c r="D102" s="15" t="s">
+        <v>109</v>
       </c>
       <c r="E102" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="103" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="103" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B103" s="4">
         <v>100</v>
       </c>
-      <c r="C103" s="17">
+      <c r="C103" s="16">
         <v>4</v>
       </c>
-      <c r="D103" s="16" t="s">
-        <v>111</v>
+      <c r="D103" s="15" t="s">
+        <v>110</v>
       </c>
       <c r="E103" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="104" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="104" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B104" s="4">
         <v>101</v>
       </c>
-      <c r="C104" s="17">
+      <c r="C104" s="16">
         <v>4</v>
       </c>
-      <c r="D104" s="16" t="s">
-        <v>112</v>
+      <c r="D104" s="15" t="s">
+        <v>111</v>
       </c>
       <c r="E104" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="105" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="105" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B105" s="4">
         <v>102</v>
       </c>
-      <c r="C105" s="17">
+      <c r="C105" s="16">
         <v>4</v>
       </c>
-      <c r="D105" s="16" t="s">
-        <v>113</v>
+      <c r="D105" s="15" t="s">
+        <v>112</v>
       </c>
       <c r="E105" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="106" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="106" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B106" s="4">
         <v>103</v>
       </c>
-      <c r="C106" s="17">
+      <c r="C106" s="16">
         <v>4</v>
       </c>
-      <c r="D106" s="16" t="s">
-        <v>114</v>
+      <c r="D106" s="15" t="s">
+        <v>113</v>
       </c>
       <c r="E106" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="107" spans="2:5" ht="14.25" x14ac:dyDescent="0.4">
+    <row r="107" spans="2:5" ht="15" x14ac:dyDescent="0.35">
       <c r="B107" s="4">
         <v>104</v>
       </c>
-      <c r="C107" s="17">
+      <c r="C107" s="16">
         <v>4</v>
       </c>
-      <c r="D107" s="16" t="s">
-        <v>115</v>
+      <c r="D107" s="15" t="s">
+        <v>114</v>
       </c>
       <c r="E107" s="4">
         <v>10</v>
